--- a/data/waza.xlsx
+++ b/data/waza.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="178" documentId="8_{F10CEDD4-43BF-4ED8-BCEF-F362456288B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E17B6C9-1F2B-4A17-AAAA-956921D0BCF7}"/>
   <bookViews>
-    <workbookView xWindow="12945" yWindow="3150" windowWidth="15435" windowHeight="11145" xr2:uid="{3B64E2FE-2656-46E5-9780-24DEB033B2C2}"/>
+    <workbookView xWindow="885" yWindow="900" windowWidth="15345" windowHeight="14490" xr2:uid="{3B64E2FE-2656-46E5-9780-24DEB033B2C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30020,10 +30020,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -73674,7 +73670,7 @@
         <v>4338</v>
       </c>
     </row>
-    <row r="2168" spans="1:6" ht="243.75" x14ac:dyDescent="0.4">
+    <row r="2168" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A2168" s="2" t="s">
         <v>1530</v>
       </c>
